--- a/Dados_Financas_P1_241021847.xlsx
+++ b/Dados_Financas_P1_241021847.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6E44D7F-11C9-4F0E-8C78-480F79467283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89C1AB9F-CCCF-4AD0-8281-81F8D22FCE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>Ano (Serão os últimos 10 anos, ex: 2014 a 2023)</t>
+    <t xml:space="preserve">Ano </t>
   </si>
   <si>
     <t>PIB Nominal (Rúpia Indonésia - IDR)</t>
@@ -53,7 +53,16 @@
     <t>Despesa Total (Nominal)</t>
   </si>
   <si>
-    <t>Fator de Deflação (usaremos para calcular os valores reais exigidos na prova)</t>
+    <t>Fator de Deflação</t>
+  </si>
+  <si>
+    <t>PIB Real</t>
+  </si>
+  <si>
+    <t>Receita Total Real</t>
+  </si>
+  <si>
+    <t>Despesa Total Real</t>
   </si>
 </sst>
 </file>
@@ -97,9 +106,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,18 +424,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="71.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,18 +457,353 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>2014</v>
+      </c>
+      <c r="B2" s="2">
+        <v>890814755533.53687</v>
+      </c>
+      <c r="C2">
+        <v>124.3861499940403</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1750366.09</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1941100.6</v>
+      </c>
+      <c r="F2" s="2">
+        <f>$C$11/C2</f>
+        <v>1.3591024422803484</v>
+      </c>
+      <c r="G2" s="2">
+        <f>B2*F2</f>
+        <v>1210708509865.0015</v>
+      </c>
+      <c r="H2" s="2">
+        <f>D2*F2</f>
+        <v>2378926.827803704</v>
+      </c>
+      <c r="I2" s="2">
+        <f>E2*F2</f>
+        <v>2638154.5661718496</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2015</v>
+      </c>
+      <c r="B3" s="2">
+        <v>860854232686.21387</v>
+      </c>
+      <c r="C3">
+        <v>132.30099074274261</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1714915.49</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2028883.753</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F10" si="0">$C$11/C3</f>
+        <v>1.2777948169070936</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G11" si="1">B3*F3</f>
+        <v>1099995076638.9773</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H11" si="2">D3*F3</f>
+        <v>2191310.1245556888</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I11" si="3">E3*F3</f>
+        <v>2592497.1436904119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="2">
+        <v>931877364037.69751</v>
+      </c>
+      <c r="C4">
+        <v>136.9656650651435</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1780829.96</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2098433.66</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>1.2342766354059962</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="1"/>
+        <v>1150194457495.458</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>2198036.8112589945</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" si="3"/>
+        <v>2590047.6374874902</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1015618744159.7339</v>
+      </c>
+      <c r="C5">
+        <v>142.182411367013</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1926989.32</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2234659.67</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1889903864858149</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="1"/>
+        <v>1207560923140.72</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>2291171.7763408376</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="3"/>
+        <v>2656988.8646975635</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1042271532988.6317</v>
+      </c>
+      <c r="C6">
+        <v>146.72989905065259</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2214097.08</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2464880.875</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1521409156315918</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>1200843678354.2649</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>2550951.8370484337</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="3"/>
+        <v>2839890.1082452992</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1119099871350.1992</v>
+      </c>
+      <c r="C7">
+        <v>151.17667278869419</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2259030.0099999998</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2590031.3640000001</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>1.1182513619613981</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>1251434955308.1855</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>2526163.3853941704</v>
+      </c>
+      <c r="I7" s="2">
+        <f>E7*F7</f>
+        <v>2896306.1003157375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1059054842698.4821</v>
+      </c>
+      <c r="C8">
+        <v>154.0790158769978</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1907538.44</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2845700.423</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0971871755574187</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>1161981391620.7539</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>2092926.7132508047</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="3"/>
+        <v>3122266.0095939217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1186509691086.7307</v>
+      </c>
+      <c r="C9">
+        <v>156.48276998491039</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2329015.33</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3076816.1189999999</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0803331271490892</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>1281825724964.4277</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>2516112.4146370683</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="3"/>
+        <v>3323986.3795019942</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1319101183380.1516</v>
+      </c>
+      <c r="C10">
+        <v>163.06985685065459</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2971534.31</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3400751.48</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0366938654859761</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>1367504104765.4949</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>3080571.3902581027</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="3"/>
+        <v>3525538.197358354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1371169301563.6216</v>
+      </c>
+      <c r="C11">
+        <v>169.0535202427499</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3131113.963</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3475717.8229999999</v>
+      </c>
+      <c r="F11" s="2">
+        <f>$C$11/C11</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>1371169301563.6216</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>3131113.963</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="3"/>
+        <v>3475717.8229999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Dados_Financas_P1_241021847.xlsx
+++ b/Dados_Financas_P1_241021847.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89C1AB9F-CCCF-4AD0-8281-81F8D22FCE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{621878ED-D653-4D10-9A39-9D71DA9FAFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indonésia (Macro)" sheetId="1" r:id="rId1"/>
     <sheet name="Betim-MG (Micro 1)" sheetId="2" r:id="rId2"/>
-    <sheet name="Volta Redonda-RJ (Micro 2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Gov. Valadares-MG (Micro 2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t xml:space="preserve">Ano </t>
   </si>
@@ -63,13 +63,34 @@
   </si>
   <si>
     <t>Despesa Total Real</t>
+  </si>
+  <si>
+    <t>Ano</t>
+  </si>
+  <si>
+    <t>População</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPCA </t>
+  </si>
+  <si>
+    <t>Receita Total Nominal (R$)</t>
+  </si>
+  <si>
+    <t>Despesa Total Nominal (R$)</t>
+  </si>
+  <si>
+    <t>Receita Total Real (R$)</t>
+  </si>
+  <si>
+    <t>Despesa Total Real (R$)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +104,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -106,10 +134,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,9 +841,279 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3381999-C755-43E1-90FD-5713781331ED}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="78.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>2014</v>
+      </c>
+      <c r="B2" s="2">
+        <v>412003</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4059.86</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1608030220.6500001</v>
+      </c>
+      <c r="F2">
+        <f>$C$11 / C2</f>
+        <v>1.6683506327804407</v>
+      </c>
+      <c r="G2" s="2">
+        <f>D2*F2</f>
+        <v>2682758236.1514993</v>
+      </c>
+      <c r="H2" s="2">
+        <f>E2*F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>2015</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2">
+        <v>4493.17</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="F3">
+        <f t="shared" ref="F3:F12" si="0">$C$11 / C3</f>
+        <v>1.5074590990325316</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G12" si="1">D3*F3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H12" si="2">E3*F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2">
+        <v>4775.7</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.4182779487823776</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2">
+        <v>4916.46</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>1.3776721462190276</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
+        <v>5100.6099999999997</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>1.3279333256218375</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
+        <v>5320.25</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1.2731112259762229</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2">
+        <v>5560.59</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1.2180847715799943</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2">
+        <v>6120.04</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1.1067362304821537</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2">
+        <v>6474.09</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>1.0462119000508181</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2">
+        <v>6773.27</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
+        <v>7100.5</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Dados_Financas_P1_241021847.xlsx
+++ b/Dados_Financas_P1_241021847.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{621878ED-D653-4D10-9A39-9D71DA9FAFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2950CAAD-0730-493E-AE53-29824A442107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indonésia (Macro)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t xml:space="preserve">Ano </t>
   </si>
@@ -65,6 +65,9 @@
     <t>Despesa Total Real</t>
   </si>
   <si>
+    <t>QUESTAO 2</t>
+  </si>
+  <si>
     <t>Ano</t>
   </si>
   <si>
@@ -85,11 +88,17 @@
   <si>
     <t>Despesa Total Real (R$)</t>
   </si>
+  <si>
+    <t>CORRELAÇÃO RECETA/DESPESA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -122,7 +131,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -130,15 +139,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -154,6 +259,1016 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Evolução da Receita e Despesa Total Real - Indonésia (2014-2023)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Indonésia (Macro)'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Receita Total Real</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Indonésia (Macro)'!$H$2:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2378926.827803704</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2191310.1245556888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2198036.8112589945</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2291171.7763408376</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2550951.8370484337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2526163.3853941704</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2092926.7132508047</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2516112.4146370683</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3080571.3902581027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3131113.963</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C3B9-4A9D-AE03-9B05E52C0E06}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Indonésia (Macro)'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Despesa Total Real</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Indonésia (Macro)'!$I$2:$I$11</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2638154.5661718496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2592497.1436904119</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2590047.6374874902</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2656988.8646975635</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2839890.1082452992</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2896306.1003157375</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3122266.0095939217</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3323986.3795019942</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3525538.197358354</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3475717.8229999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C3B9-4A9D-AE03-9B05E52C0E06}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1234858504"/>
+        <c:axId val="1246631944"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1234858504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1246631944"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1246631944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1234858504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2647950</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0EE6121-5FBE-7F28-AFF3-627BC2F700EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -834,57 +1949,145 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="6"/>
+      <c r="C21" s="7"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="6"/>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="6"/>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="6"/>
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="6"/>
+      <c r="C25" s="7"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="6"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6"/>
+      <c r="C27" s="7"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6"/>
+      <c r="C28" s="7"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6"/>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="6"/>
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="6"/>
+      <c r="C31" s="7"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="6"/>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6"/>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="6"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="6"/>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6"/>
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="6"/>
+      <c r="C37" s="7"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:C20"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3381999-C755-43E1-90FD-5713781331ED}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="78.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>2014</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>412003</v>
       </c>
       <c r="C2" s="2">
@@ -893,8 +2096,11 @@
       <c r="D2" s="2">
         <v>1608030220.6500001</v>
       </c>
-      <c r="F2">
-        <f>$C$11 / C2</f>
+      <c r="E2" s="2">
+        <v>1302413809.52</v>
+      </c>
+      <c r="F2" s="5">
+        <f>$C$11/C2</f>
         <v>1.6683506327804407</v>
       </c>
       <c r="G2" s="2">
@@ -903,215 +2109,316 @@
       </c>
       <c r="H2" s="2">
         <f>E2*F2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>2172882903.2546763</v>
+      </c>
+      <c r="K2">
+        <f>CORREL(G2:G11, H2:H11)</f>
+        <v>0.82845211490438542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2015</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="4">
+        <v>412003</v>
+      </c>
       <c r="C3" s="2">
         <v>4493.17</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="F3">
-        <f t="shared" ref="F3:F12" si="0">$C$11 / C3</f>
+      <c r="D3" s="2">
+        <v>1570000000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1308832859.3499999</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F11" si="0">$C$11/C3</f>
         <v>1.5074590990325316</v>
       </c>
       <c r="G3" s="2">
         <f t="shared" ref="G3:G12" si="1">D3*F3</f>
-        <v>0</v>
+        <v>2366710785.4810748</v>
       </c>
       <c r="H3" s="2">
         <f t="shared" ref="H3:H12" si="2">E3*F3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>1973012002.939923</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2016</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="4">
+        <v>417307</v>
+      </c>
       <c r="C4" s="2">
         <v>4775.7</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="F4">
+      <c r="D4" s="2">
+        <v>1780000000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1393353773.3</v>
+      </c>
+      <c r="F4" s="5">
         <f t="shared" si="0"/>
         <v>1.4182779487823776</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2524534748.8326321</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>1976162931.5241098</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2017</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="4">
+        <v>422354</v>
+      </c>
       <c r="C5" s="2">
         <v>4916.46</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="F5">
+      <c r="D5" s="2">
+        <v>1780000000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1311537940.04</v>
+      </c>
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>1.3776721462190276</v>
       </c>
       <c r="G5" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2452256420.2698689</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>1806869288.702589</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>2018</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="4">
+        <v>422354</v>
+      </c>
       <c r="C6" s="2">
         <v>5100.6099999999997</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="F6">
+      <c r="D6" s="2">
+        <v>1780000000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1477402214.5</v>
+      </c>
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>1.3279333256218375</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2363721319.6068707</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>1961891635.9820523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>2019</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="4">
+        <v>432575</v>
+      </c>
       <c r="C7" s="2">
         <v>5320.25</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="F7">
+      <c r="D7" s="2">
+        <v>1990831542.55</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1579609741.8</v>
+      </c>
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
         <v>1.2731112259762229</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2534549985.8479657</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>2011018894.9469829</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>2020</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="4">
+        <v>439340</v>
+      </c>
       <c r="C8" s="2">
         <v>5560.59</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="F8">
+      <c r="D8" s="2">
+        <v>2369478082.0999999</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1790222832.3699999</v>
+      </c>
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
         <v>1.2180847715799943</v>
       </c>
       <c r="G8" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2886225168.3985815</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>2180643169.8447018</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>2021</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="4">
+        <v>444784</v>
+      </c>
       <c r="C9" s="2">
         <v>6120.04</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="F9">
+      <c r="D9" s="2">
+        <v>2669443140.79</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1943330452.02</v>
+      </c>
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
         <v>1.1067362304821537</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2954369439.1243658</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>2150754219.0497947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>2022</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="4">
+        <v>450024</v>
+      </c>
       <c r="C10" s="2">
         <v>6474.09</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="F10">
+      <c r="D10" s="2">
+        <v>2864681686.3499999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2229978284.04</v>
+      </c>
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
         <v>1.0462119000508181</v>
       </c>
       <c r="G10" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2997064070.1170154</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>2333029817.6175513</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>2023</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="4">
+        <v>450024</v>
+      </c>
       <c r="C11" s="2">
         <v>6773.27</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="F11">
+      <c r="D11" s="2">
+        <v>2952757996.2600002</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2563906912.4499998</v>
+      </c>
+      <c r="F11" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2952757996.2600002</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2">
-        <v>7100.5</v>
-      </c>
+        <v>2563906912.4499998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="4"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="4"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="4"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="4"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="4"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="4"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="4"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1120,9 +2427,379 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B96FA1-E67E-43E5-9274-07EE57CC8201}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>2014</v>
+      </c>
+      <c r="B2" s="4">
+        <v>276995</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4059.86</v>
+      </c>
+      <c r="D2" s="2">
+        <v>710327301.38999999</v>
+      </c>
+      <c r="E2" s="2">
+        <v>671828796.32000005</v>
+      </c>
+      <c r="F2" s="5">
+        <f>$C$11/C2</f>
+        <v>1.6683506327804407</v>
+      </c>
+      <c r="G2" s="2">
+        <f>D2*F2</f>
+        <v>1185075002.7552292</v>
+      </c>
+      <c r="H2" s="2">
+        <f>E2*F2</f>
+        <v>1120845997.4605939</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>2015</v>
+      </c>
+      <c r="B3" s="4">
+        <v>276995</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4493.17</v>
+      </c>
+      <c r="D3" s="2">
+        <v>743000000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>727007000.19000006</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F11" si="0">$C$11/C3</f>
+        <v>1.5074590990325316</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G11" si="1">D3*F3</f>
+        <v>1120042110.581171</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H11" si="2">E3*F3</f>
+        <v>1095933317.4967611</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4">
+        <v>278363</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4775.7</v>
+      </c>
+      <c r="D4" s="2">
+        <v>772000000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>732963068.20000005</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>1.4182779487823776</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="1"/>
+        <v>1094910576.4599955</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>1039545356.8999339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="4">
+        <v>279665</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4916.46</v>
+      </c>
+      <c r="D5" s="2">
+        <v>814000000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>759413034.67999995</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>1.3776721462190276</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="1"/>
+        <v>1121425127.0222883</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>1046222185.3543004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="4">
+        <v>279665</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5100.6099999999997</v>
+      </c>
+      <c r="D6" s="2">
+        <v>824000000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>838267941.97000003</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>1.3279333256218375</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>1094217060.3123941</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>1113163935.9423957</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="4">
+        <v>278685</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5320.25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>931296028.39999998</v>
+      </c>
+      <c r="E7" s="2">
+        <v>931177855.74000001</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.2731112259762229</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>1185643428.4631114</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>1185492981.523062</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="4">
+        <v>279885</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5560.59</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1108011257.28</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1037491950.46</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.2180847715799943</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>1349651639.231971</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>1263753145.492152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="4">
+        <v>281046</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6120.04</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1251484593.0799999</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1153807933.22</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>1.1067362304821537</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>1385063341.0518513</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>1276961042.7123075</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="4">
+        <v>282164</v>
+      </c>
+      <c r="C10" s="2">
+        <v>6474.09</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1436931777.8699999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1453351432.3800001</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0462119000508181</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>1503335125.5687728</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>1520513563.511858</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="4">
+        <v>282164</v>
+      </c>
+      <c r="C11" s="2">
+        <v>6773.27</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1547441182.0999999</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1612163303.28</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>1547441182.0999999</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>1612163303.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="4"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="4"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="4"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="4"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16" s="4"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="4"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="4"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>